--- a/sample_excel_files/event_students_bulk_upload.xlsx
+++ b/sample_excel_files/event_students_bulk_upload.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Event Students" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +28,16 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,8 +46,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3D3D3"/>
+        <bgColor rgb="00D3D3D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,12 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,320 +442,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reg No</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+          <t>RegNo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <f>== Method 1: For Registered Students (Use RegNo) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>12101001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>12101002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>12101003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>12101004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>12101005</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <f>== Method 2: For External/Non-Registered Students ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>RegNo</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S2024001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rahul Sharma</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>rahul.sharma@pict.edu</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S2024002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Priya Patel</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>priya.patel@pict.edu</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9876543211</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>EXT001</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sanjay Mehta</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sanjay.mehta@coep.edu</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9123456789</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>External Student 1</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>external1@example.com</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>9876543220</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>EXT002</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Neha Kulkarni</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>neha.k@vit.edu</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9123456790</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S2024005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rohan Joshi</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>rohan.joshi@pict.edu</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9876543214</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EXT003</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arjun Reddy</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>arjun.r@manipal.edu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9123456791</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S2024008</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pooja Reddy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pooja.reddy@pict.edu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>9876543217</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EXT004</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Simran Kaur</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>simran.k@amity.edu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>9123456792</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Event Student Upload Instructions</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Format:</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Reg No | Name | Email | Mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Note 1:</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>For PICT students, use existing Reg No (system will fetch details)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Note 2:</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>For external college students, provide all details manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Note 3:</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>External student Reg No can be any unique identifier (e.g., EXT001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Example 1 (PICT):</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>S2024001 | (Name auto-filled) | (Email auto-filled) | (Mobile auto-filled)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Example 2 (External):</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EXT001 | Sanjay Mehta | sanjay@coep.edu | 9123456789</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>External Student 2</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>external2@example.com</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>9876543221</t>
         </is>
       </c>
     </row>

--- a/sample_excel_files/event_students_bulk_upload.xlsx
+++ b/sample_excel_files/event_students_bulk_upload.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PICT Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Students" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Help &amp; Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +30,48 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -46,14 +83,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
-        <bgColor rgb="00D3D3D3"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,14 +106,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,10 +511,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -454,123 +523,634 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RegNo</t>
+          <t>Reg No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <f>== Method 1: For Registered Students (Use RegNo) ===</f>
-        <v/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Instructions: Add registration numbers (GRN) of PICT students here</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>12101001</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Reg No</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Name (Auto-filled)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Email (Auto-filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12101001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>12101002</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>12101003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>12101004</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>12101005</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ External ID auto-generated as: EventName_exe001, exe002, etc. | Fill columns below only</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>✓ Duplicates skipped (checked by email/mobile) | ✓ QR codes auto-emailed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>12101003</t>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>12101004</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Raj Singh</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>raj.singh@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>9876543210</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>12101005</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>priya.p@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>amit.k@example.com</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>9876543212</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Neha Sharma</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>neha.sharma@email.com</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>9876543213</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
-        <f>== Method 2: For External/Non-Registered Students ===</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>RegNo</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>EXT001</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>External Student 1</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>external1@example.com</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>9876543220</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>EXT002</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>External Student 2</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>external2@example.com</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>9876543221</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Vikram Desai</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>v.desai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>9876543214</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>TECH FEST 2026 - EVENT STUDENT UPLOAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>📋 UPLOADING STUDENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>✓ Use 'PICT Students' sheet for PICT registered students (only Reg No needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>✓ Use 'External Students' sheet for students from other colleges (3 columns only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>✓ You can upload them separately or mix both types</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>🚀 EXTERNAL STUDENT FORMAT (Simple &amp; Clear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Column 1: Full Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Column 2: Email Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Column 3: Mobile Number (10 digits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>✅ External ID auto-generated as:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Format: EventName_exe001, EventName_exe002, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Example: Tech_Fest_2026_exe001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>✓ DUPLICATE CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>✓ Same student won't be added twice (checked by email &amp; mobile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>✓ If duplicate found: You get 'skipped' message with existing Student ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>📧 QR CODE EMAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>✓ All external students auto-receive QR code email after upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>✓ Email = Main delivery method for QR code passes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>✓ Can resend anytime using 'Resend Email' button in Admin Events tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ REQUIRED FIELDS FOR EXTERNAL STUDENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>✓ Full Name: Complete name of student</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>✓ Email: Valid email (MUST be correct - QR sent here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>✓ Mobile: 10-digit phone number</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>❌ NO NEED TO PROVIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>✗ External ID: Auto-generated by system</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>✗ Any other identifier: System handles registration</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>📊 PICT STUDENT FORMAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>✓ Only column 1: PICT Registration Number (Reg No/GRN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>✓ Name, Email, Mobile auto-filled from PICT system</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>✓ Example: 12101001</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>⚡ BULK UPLOAD TIPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>✓ Prepare data in correct Excel sheet (PICT vs External)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>✓ No empty rows in middle of data</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>✓ Double-check email addresses (QR codes sent there)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>✓ For external students: Name | Email | Mobile (3 columns only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>🎯 WORKFLOW EXAMPLE - Adding External Students</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>1. Admin Dashboard → Events Tab → Select Event (Tech Fest 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>2. Click 'View Students' → External Student tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>3. Enter: Name | Email | Mobile (system generates ID automatically)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>4. Click 'Add &amp; Send QR Email' → Student gets QR code via email ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>🎯 BULK UPLOAD EXAMPLE - Excel Format</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Sheet: 'External Students'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Row 1: Full Name | Email | Mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>Row 2: Raj Singh | raj.singh@gmail.com | 9876543210</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>Row 3: Priya Patel | priya.p@gmail.com | 9876543211</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="8" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Result: Both students get Tech_Fest_2026_exe001 &amp; exe002 IDs with QR emails ✓</t>
         </is>
       </c>
     </row>
